--- a/data/trans_dic/IQ2601_R2-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/IQ2601_R2-Habitat-trans_dic.xlsx
@@ -533,7 +533,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -541,7 +541,7 @@
       <c r="F1" s="3" t="n"/>
       <c r="G1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="H1" s="3" t="n"/>
@@ -649,44 +649,44 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>50,39%</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>47,81%</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>64,69%</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>68,58%</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
           <t>60,12%</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>47,29%</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="I4" s="2" t="inlineStr">
         <is>
           <t>61,31%</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
+      <c r="J4" s="2" t="inlineStr">
         <is>
           <t>78,11%</t>
         </is>
       </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>50,39%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>47,81%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>64,69%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>67,22%</t>
-        </is>
-      </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
           <t>55,02%</t>
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>71,96%</t>
+          <t>72,97%</t>
         </is>
       </c>
     </row>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>53,49; 67,13</t>
+          <t>43,84; 57,12</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>39,85; 53,92</t>
+          <t>40,48; 54,85</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>54,17; 68,65</t>
+          <t>57,42; 71,04</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>65,67; 89,46</t>
+          <t>54,47; 82,84</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>43,54; 57,03</t>
+          <t>53,16; 67,75</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>41,05; 54,56</t>
+          <t>40,23; 54,68</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>58,09; 71,47</t>
+          <t>53,8; 68,49</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>51,65; 80,26</t>
+          <t>64,05; 87,42</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>50,14; 59,95</t>
+          <t>50,48; 59,71</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>41,83; 52,73</t>
+          <t>42,54; 52,47</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>57,97; 68,1</t>
+          <t>57,7; 67,93</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>63,02; 81,22</t>
+          <t>63,12; 81,02</t>
         </is>
       </c>
     </row>
@@ -789,42 +789,42 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>64,46%</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>49,65%</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>67,69%</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>80,48%</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
           <t>63,55%</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="H6" s="2" t="inlineStr">
         <is>
           <t>54,23%</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="I6" s="2" t="inlineStr">
         <is>
           <t>69,17%</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>67,03%</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>64,46%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>49,65%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>67,69%</t>
-        </is>
-      </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>81,02%</t>
+          <t>65,8%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>75,62%</t>
+          <t>74,59%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>58,68; 68,79</t>
+          <t>58,61; 69,29</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>47,74; 59,43</t>
+          <t>44,13; 55,26</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>64,02; 74,34</t>
+          <t>62,33; 72,52</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>53,14; 79,06</t>
+          <t>69,69; 88,46</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>58,77; 69,32</t>
+          <t>57,65; 68,56</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>44,38; 55,56</t>
+          <t>47,71; 59,89</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>62,63; 72,47</t>
+          <t>64,02; 73,75</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>70,26; 88,99</t>
+          <t>52,15; 78,29</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>59,96; 67,81</t>
+          <t>60,41; 67,76</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>47,67; 55,87</t>
+          <t>48,01; 55,49</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>64,96; 72,2</t>
+          <t>64,52; 71,66</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>66,77; 82,57</t>
+          <t>65,48; 81,9</t>
         </is>
       </c>
     </row>
@@ -929,42 +929,42 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>78,49%</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>53,27%</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>65,44%</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>64,31%</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
           <t>78,74%</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>54,03%</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="I8" s="2" t="inlineStr">
         <is>
           <t>60,03%</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>76,17%</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>78,49%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>53,27%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>65,44%</t>
-        </is>
-      </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>63,81%</t>
+          <t>73,1%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>68,79%</t>
+          <t>67,77%</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>73,03; 83,78</t>
+          <t>72,45; 83,46</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>47,1; 60,4</t>
+          <t>46,76; 59,62</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>53,89; 66,4</t>
+          <t>59,29; 70,99</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>61,47; 87,72</t>
+          <t>48,28; 76,27</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>71,6; 83,15</t>
+          <t>72,89; 84,01</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>46,76; 59,95</t>
+          <t>46,6; 59,97</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>59,08; 70,96</t>
+          <t>53,96; 65,94</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>49,71; 75,75</t>
+          <t>57,41; 86,77</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>74,41; 82,32</t>
+          <t>74,92; 82,69</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>49,16; 58,1</t>
+          <t>48,99; 58,01</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>58,42; 67,59</t>
+          <t>58,22; 67,06</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>57,36; 78,27</t>
+          <t>58,17; 77,16</t>
         </is>
       </c>
     </row>
@@ -1069,42 +1069,42 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>67,97%</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>46,04%</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>59,49%</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>75,89%</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
           <t>69,97%</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>53,24%</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="I10" s="2" t="inlineStr">
         <is>
           <t>63,71%</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>62,72%</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>67,97%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>46,04%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>59,49%</t>
-        </is>
-      </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>75,69%</t>
+          <t>60,76%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>69,48%</t>
+          <t>68,41%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>64,16; 75,43</t>
+          <t>62,76; 72,96</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>47,3; 59,7</t>
+          <t>39,81; 52,31</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>57,85; 69,33</t>
+          <t>53,25; 65,07</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>50,2; 75,01</t>
+          <t>62,18; 85,49</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>62,54; 72,86</t>
+          <t>64,71; 74,92</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>39,52; 52,16</t>
+          <t>47,51; 59,0</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>53,94; 65,37</t>
+          <t>58,32; 69,59</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>64,29; 86,04</t>
+          <t>47,95; 72,08</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>65,08; 72,88</t>
+          <t>64,94; 72,5</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>45,86; 53,93</t>
+          <t>45,52; 54,09</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>57,56; 65,81</t>
+          <t>57,34; 65,47</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>60,57; 77,2</t>
+          <t>58,68; 76,55</t>
         </is>
       </c>
     </row>
@@ -1209,42 +1209,42 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>65,39%</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>49,06%</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>64,33%</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>73,38%</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
           <t>67,86%</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="H12" s="2" t="inlineStr">
         <is>
           <t>52,5%</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="I12" s="2" t="inlineStr">
         <is>
           <t>64,06%</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>69,68%</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>65,39%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>49,06%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>64,33%</t>
-        </is>
-      </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>73,13%</t>
+          <t>68,06%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>71,66%</t>
+          <t>71,05%</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>65,02; 70,61</t>
+          <t>62,22; 68,07</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>49,05; 55,47</t>
+          <t>45,83; 52,09</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>61,16; 66,79</t>
+          <t>61,19; 67,41</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>62,91; 75,68</t>
+          <t>67,04; 78,97</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>62,17; 67,92</t>
+          <t>65,16; 70,86</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>45,69; 52,07</t>
+          <t>49,44; 55,67</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>61,56; 67,25</t>
+          <t>60,93; 66,86</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>67,0; 79,36</t>
+          <t>61,36; 74,37</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>64,67; 68,55</t>
+          <t>64,54; 68,67</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>48,65; 53,02</t>
+          <t>48,66; 53,14</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>61,99; 66,26</t>
+          <t>62,25; 66,12</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>67,07; 75,65</t>
+          <t>66,6; 75,37</t>
         </is>
       </c>
     </row>
@@ -1393,7 +1393,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -1401,7 +1401,7 @@
       <c r="F1" s="3" t="n"/>
       <c r="G1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="H1" s="3" t="n"/>
@@ -1509,42 +1509,42 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>110</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>98</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>127</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
           <t>119</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>90</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="I4" s="2" t="inlineStr">
         <is>
           <t>113</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
+      <c r="J4" s="2" t="inlineStr">
         <is>
           <t>38</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>110</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>98</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>127</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>32</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -1577,42 +1577,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>74495</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>70765</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>95303</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>22268</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
           <t>80567</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="H5" s="2" t="inlineStr">
         <is>
           <t>65252</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="I5" s="2" t="inlineStr">
         <is>
           <t>80417</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>21242</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>74495</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>70765</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>95303</t>
-        </is>
-      </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>23684</t>
+          <t>21666</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -1632,7 +1632,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>44926</t>
+          <t>43933</t>
         </is>
       </c>
     </row>
@@ -1645,62 +1645,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>71689; 89957</t>
+          <t>64808; 84436</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>54989; 74403</t>
+          <t>59912; 81186</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>71054; 90045</t>
+          <t>84592; 104648</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>17858; 24327</t>
+          <t>17689; 26899</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>64369; 84298</t>
+          <t>71243; 90789</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>60753; 80761</t>
+          <t>55517; 75453</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>85574; 105285</t>
+          <t>70559; 89828</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>18197; 28280</t>
+          <t>17765; 24246</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>141301; 168964</t>
+          <t>142267; 168279</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>119647; 150822</t>
+          <t>121674; 150066</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>161432; 189632</t>
+          <t>160676; 189172</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>39345; 50704</t>
+          <t>38003; 48783</t>
         </is>
       </c>
     </row>
@@ -1717,42 +1717,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>203</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>157</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>223</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>68</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
           <t>196</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="H7" s="2" t="inlineStr">
         <is>
           <t>168</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="I7" s="2" t="inlineStr">
         <is>
           <t>228</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
+      <c r="J7" s="2" t="inlineStr">
         <is>
           <t>44</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>203</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>157</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>223</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>68</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
@@ -1785,42 +1785,42 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>135101</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>108092</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>150131</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>47313</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
           <t>122450</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>107335</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="I8" s="2" t="inlineStr">
         <is>
           <t>141649</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>26352</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>135101</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>108092</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>150131</t>
-        </is>
-      </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>50655</t>
+          <t>25902</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -1840,7 +1840,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>77007</t>
+          <t>73216</t>
         </is>
       </c>
     </row>
@@ -1853,62 +1853,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>113069; 132545</t>
+          <t>122846; 145237</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>94497; 117632</t>
+          <t>96077; 120319</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>131097; 152239</t>
+          <t>138245; 160839</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>20891; 31083</t>
+          <t>40970; 52010</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>123180; 145292</t>
+          <t>111092; 132105</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>96620; 120971</t>
+          <t>94440; 118533</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>138914; 160736</t>
+          <t>131110; 151029</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>43928; 55636</t>
+          <t>20529; 30816</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>241213; 272783</t>
+          <t>243005; 272575</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>198149; 232215</t>
+          <t>199555; 230656</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>277094; 307974</t>
+          <t>275236; 305676</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>67998; 84087</t>
+          <t>64272; 80389</t>
         </is>
       </c>
     </row>
@@ -1925,42 +1925,42 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>175</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>132</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>159</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
           <t>172</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>129</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="I10" s="2" t="inlineStr">
         <is>
           <t>150</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
+      <c r="J10" s="2" t="inlineStr">
         <is>
           <t>32</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>175</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>132</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>159</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>36</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1993,42 +1993,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>112539</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>84377</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>108309</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>26694</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
           <t>103636</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="H11" s="2" t="inlineStr">
         <is>
           <t>80943</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
+      <c r="I11" s="2" t="inlineStr">
         <is>
           <t>91812</t>
         </is>
       </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>22701</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>112539</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>84377</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>108309</t>
-        </is>
-      </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>28196</t>
+          <t>19678</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -2048,7 +2048,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>50897</t>
+          <t>46371</t>
         </is>
       </c>
     </row>
@@ -2061,62 +2061,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>96117; 110263</t>
+          <t>103872; 119667</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>70563; 90490</t>
+          <t>74076; 94441</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>82423; 101553</t>
+          <t>98123; 117499</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>18322; 26145</t>
+          <t>20038; 31659</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>102657; 119218</t>
+          <t>95929; 110568</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>74077; 94972</t>
+          <t>69819; 89840</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>97787; 117445</t>
+          <t>82525; 100847</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>21966; 33474</t>
+          <t>15455; 23359</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>204632; 226366</t>
+          <t>206027; 227378</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>151527; 179091</t>
+          <t>150987; 178792</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>186055; 215254</t>
+          <t>185388; 213550</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>42443; 57911</t>
+          <t>39804; 52794</t>
         </is>
       </c>
     </row>
@@ -2133,42 +2133,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>203</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>124</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>172</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>49</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
           <t>187</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="H13" s="2" t="inlineStr">
         <is>
           <t>138</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
+      <c r="I13" s="2" t="inlineStr">
         <is>
           <t>178</t>
         </is>
       </c>
-      <c r="F13" s="2" t="inlineStr">
+      <c r="J13" s="2" t="inlineStr">
         <is>
           <t>42</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>203</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>124</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>172</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>49</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
@@ -2201,42 +2201,42 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>140338</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>92980</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>120605</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>34603</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
           <t>144384</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="H14" s="2" t="inlineStr">
         <is>
           <t>107577</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="I14" s="2" t="inlineStr">
         <is>
           <t>130388</t>
         </is>
       </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>28689</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>140338</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>92980</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>120605</t>
-        </is>
-      </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>37714</t>
+          <t>27060</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2256,7 +2256,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>66403</t>
+          <t>61663</t>
         </is>
       </c>
     </row>
@@ -2269,62 +2269,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>132403; 155655</t>
+          <t>129569; 150646</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>95560; 120616</t>
+          <t>80404; 105630</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>118387; 141883</t>
+          <t>107949; 131916</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>22960; 34312</t>
+          <t>28351; 38976</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>129128; 150437</t>
+          <t>133520; 154594</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>79811; 105339</t>
+          <t>95992; 119199</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>109354; 132527</t>
+          <t>119352; 142412</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>32036; 42872</t>
+          <t>21357; 32102</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>268676; 300872</t>
+          <t>268092; 299279</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>185250; 217855</t>
+          <t>183902; 218528</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>234498; 268105</t>
+          <t>233594; 266696</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>57883; 73777</t>
+          <t>52892; 68995</t>
         </is>
       </c>
     </row>
@@ -2341,42 +2341,42 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>691</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>511</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>681</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>185</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
           <t>674</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="H16" s="2" t="inlineStr">
         <is>
           <t>525</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
+      <c r="I16" s="2" t="inlineStr">
         <is>
           <t>669</t>
         </is>
       </c>
-      <c r="F16" s="2" t="inlineStr">
+      <c r="J16" s="2" t="inlineStr">
         <is>
           <t>156</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>691</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>511</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>681</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>185</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -2409,42 +2409,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>462474</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>356214</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>474348</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>130878</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
           <t>451037</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="H17" s="2" t="inlineStr">
         <is>
           <t>361108</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
+      <c r="I17" s="2" t="inlineStr">
         <is>
           <t>444266</t>
         </is>
       </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>98984</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>462474</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>356214</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>474348</t>
-        </is>
-      </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>140248</t>
+          <t>94305</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -2464,7 +2464,7 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>239232</t>
+          <t>225183</t>
         </is>
       </c>
     </row>
@@ -2477,62 +2477,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>432164; 469291</t>
+          <t>440089; 481463</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>337344; 381526</t>
+          <t>332768; 378199</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>424179; 463217</t>
+          <t>451187; 497019</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>89370; 107503</t>
+          <t>119578; 140854</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>439742; 480392</t>
+          <t>433101; 470992</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>331716; 378087</t>
+          <t>340065; 382882</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>453926; 495865</t>
+          <t>422565; 463696</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>128483; 152196</t>
+          <t>85022; 103047</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>887289; 940472</t>
+          <t>885396; 942134</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>687891; 749600</t>
+          <t>687930; 751363</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>887063; 948036</t>
+          <t>890646; 946107</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>223897; 252531</t>
+          <t>211054; 238878</t>
         </is>
       </c>
     </row>
